--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M116"/>
+  <dimension ref="A1:M117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6553,7 +6553,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>4285-195-CM26</t>
+          <t>5586-2314-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6578,12 +6578,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4183.61</v>
+        <v>1939.68</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5586-2314-CM26</t>
+          <t>4285-195-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1939.68</v>
+        <v>4183.61</v>
       </c>
     </row>
     <row r="103">
@@ -7346,7 +7346,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4179-888-CM26</t>
+          <t>3494-235-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7366,17 +7366,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1910.99</v>
+        <v>6538.24</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3494-235-CM26</t>
+          <t>4179-888-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7427,17 +7427,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6538.24</v>
+        <v>1910.99</v>
       </c>
     </row>
     <row r="116">
@@ -7524,6 +7524,67 @@
       </c>
       <c r="M116" s="2" t="n">
         <v>736.37</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>5586-2584-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>10193.3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M117"/>
+  <dimension ref="A1:M123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2388-369-CM25</t>
+          <t>3921-660-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>20481.88</v>
+        <v>63286.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1658-4808-CM25</t>
+          <t>3887-190-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8498.98</v>
+        <v>2199.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1658-4911-CM25</t>
+          <t>3708-312-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>14443.21</v>
+        <v>10831.38</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2387-488-CM25</t>
+          <t>3477-352-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2645.37</v>
+        <v>3675.55</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4285-262-CM25</t>
+          <t>514847-1074-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2882.18</v>
+        <v>7358.73</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3887-523-CM25</t>
+          <t>2548-628-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2387.14</v>
+        <v>8050.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2389-727-CM25</t>
+          <t>2388-369-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9480.49</v>
+        <v>20481.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1658-5413-CM25</t>
+          <t>1658-4808-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2544.7</v>
+        <v>8498.98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2388-397-CM25</t>
+          <t>1658-4911-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13132.25</v>
+        <v>14443.21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2388-398-CM25</t>
+          <t>2387-488-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>10124.52</v>
+        <v>2645.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2388-399-CM25</t>
+          <t>4285-262-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5062.26</v>
+        <v>2882.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>986278-2016-CM25</t>
+          <t>2389-727-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>65.148.017-5</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2677.5</v>
+        <v>9480.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>986278-2017-CM25</t>
+          <t>3887-523-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,22 +1261,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>65.148.017-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3318.49</v>
+        <v>2387.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3933-137-CM25</t>
+          <t>1658-5413-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6924.35</v>
+        <v>2544.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3933-138-CM25</t>
+          <t>2388-397-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5035.89</v>
+        <v>13132.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3933-139-CM25</t>
+          <t>2388-398-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9267.719999999999</v>
+        <v>10124.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>514848-1618-CM25</t>
+          <t>2388-399-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,22 +1505,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3688.62</v>
+        <v>5062.26</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5586-4058-CM25</t>
+          <t>986278-2016-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,22 +1566,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>17164.56</v>
+        <v>2677.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5586-4059-CM25</t>
+          <t>986278-2017-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>23526</v>
+        <v>3318.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>514848-1630-CM25</t>
+          <t>3933-137-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,28 +1728,28 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3736.6</v>
+        <v>6924.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2546-1037-CM25</t>
+          <t>3933-138-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,28 +1789,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>10652.57</v>
+        <v>5035.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3921-1361-CM25</t>
+          <t>3933-139-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,43 +1850,43 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>852.58</v>
+        <v>9267.719999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3710-1860-CM25</t>
+          <t>514848-1618-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.359.312-6</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,28 +1911,28 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7257.74</v>
+        <v>3688.62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5586-4381-CM25</t>
+          <t>5586-4058-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,43 +1972,43 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>2454.97</v>
+        <v>17164.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4179-2403-CM25</t>
+          <t>5586-4059-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2033,43 +2033,43 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>784.2</v>
+        <v>23526</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4285-342-CM25</t>
+          <t>514848-1630-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3237.23</v>
+        <v>3736.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>655-2348-CM25</t>
+          <t>2546-1037-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.821.000-6</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>9816.360000000001</v>
+        <v>10652.57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1658-60-CM26</t>
+          <t>3921-1361-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,27 +2171,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3099.95</v>
+        <v>852.58</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3836-34-CM26</t>
+          <t>3710-1860-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t xml:space="preserve">AURA XD SPA </t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.359.312-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>69969.62</v>
+        <v>7257.74</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3477-75-CM26</t>
+          <t>5586-4381-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,27 +2293,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2323,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>22700.92</v>
+        <v>2454.97</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2387-34-CM26</t>
+          <t>4179-2403-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2354,27 +2354,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>7263.68</v>
+        <v>784.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4179-61-CM26</t>
+          <t>4285-342-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2415,27 +2415,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1239.92</v>
+        <v>3237.23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>4179-62-CM26</t>
+          <t>655-2348-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2476,27 +2476,27 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>61.821.000-6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IX REGION</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>869.1799999999999</v>
+        <v>9816.360000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2548-65-CM26</t>
+          <t>1658-60-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2537,27 +2537,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>7408.42</v>
+        <v>3099.95</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4179-99-CM26</t>
+          <t>3836-34-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2598,27 +2598,27 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE TOLTEN</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>376.9</v>
+        <v>69969.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3921-91-CM26</t>
+          <t>3477-75-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2689,12 +2689,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>4848.06</v>
+        <v>22700.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2546-141-CM26</t>
+          <t>2387-34-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2100.11</v>
+        <v>7263.68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4112-14-CM26</t>
+          <t>4179-61-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2022.11</v>
+        <v>1239.92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4112-15-CM26</t>
+          <t>4179-62-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>COMPUNOW SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.218.816-K</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>11797.89</v>
+        <v>869.1799999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4284-92-CM26</t>
+          <t>2548-65-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,22 +2908,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2342.28</v>
+        <v>7408.42</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4179-179-CM26</t>
+          <t>4179-99-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2964,12 +2964,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3062.58</v>
+        <v>376.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3495-36-CM26</t>
+          <t>3921-91-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>17088.4</v>
+        <v>4848.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>765-69-CM26</t>
+          <t>2546-141-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,27 +3086,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1234.53</v>
+        <v>2100.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2547-30-CM26</t>
+          <t>4112-14-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,27 +3147,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>27307.58</v>
+        <v>2022.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>765-73-CM26</t>
+          <t>4112-15-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUNOW SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.218.816-K</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>19197.08</v>
+        <v>11797.89</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4284-115-CM26</t>
+          <t>4284-92-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1304.24</v>
+        <v>2342.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3151-173-CM26</t>
+          <t>4179-179-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>10350.98</v>
+        <v>3062.58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>765-79-CM26</t>
+          <t>765-69-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>6934.73</v>
+        <v>1234.53</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1658-739-CM26</t>
+          <t>3495-36-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>6640.06</v>
+        <v>17088.4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>765-81-CM26</t>
+          <t>2547-30-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,22 +3518,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>68338.73</v>
+        <v>27307.58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3922-178-CM26</t>
+          <t>765-73-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,22 +3579,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>685.4400000000001</v>
+        <v>19197.08</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3518-46-CM26</t>
+          <t>4284-115-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,22 +3640,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,12 +3665,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8003.94</v>
+        <v>1304.24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2736-90-CM26</t>
+          <t>3151-173-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,12 +3711,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>25579.05</v>
+        <v>10350.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3151-185-CM26</t>
+          <t>765-79-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1543.57</v>
+        <v>6934.73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>722-28-CM26</t>
+          <t>1658-739-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>12762.75</v>
+        <v>6640.06</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>4179-315-CM26</t>
+          <t>765-81-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>660.45</v>
+        <v>68338.73</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3922-225-CM26</t>
+          <t>3922-178-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>7856.98</v>
+        <v>685.4400000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3485-262-CM26</t>
+          <t>3518-46-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>10682.75</v>
+        <v>8003.94</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3212-43-CM26</t>
+          <t>2736-90-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4062,27 +4062,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.180.100-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1877.82</v>
+        <v>25579.05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3922-238-CM26</t>
+          <t>3151-185-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3102.29</v>
+        <v>1543.57</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1658-724-CM26</t>
+          <t>722-28-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4184,27 +4184,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>19010.25</v>
+        <v>12762.75</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1028897-246-CM26</t>
+          <t>4179-315-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>14921.53</v>
+        <v>660.45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>5586-907-CM26</t>
+          <t>3212-43-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,22 +4311,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4336,12 +4336,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4351,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>971.85</v>
+        <v>1877.82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3708-141-CM26</t>
+          <t>3485-262-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>14389.77</v>
+        <v>10682.75</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3751-101-CM26</t>
+          <t>3922-225-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,22 +4433,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>8701.049999999999</v>
+        <v>7856.98</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3705-180-CM26</t>
+          <t>3922-238-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4504,12 +4504,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>10256.61</v>
+        <v>3102.29</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>4322-263-CM26</t>
+          <t>1658-724-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>13546.96</v>
+        <v>19010.25</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4322-264-CM26</t>
+          <t>1028897-246-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,22 +4616,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3412.44</v>
+        <v>14921.53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>722-43-CM26</t>
+          <t>5586-907-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4672,27 +4672,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3342.12</v>
+        <v>971.85</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3608-252-CM26</t>
+          <t>3708-141-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1589.94</v>
+        <v>14389.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>4179-491-CM26</t>
+          <t>3751-101-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>96.39</v>
+        <v>8701.049999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5586-1311-CM26</t>
+          <t>3705-180-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4900,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>28915.22</v>
+        <v>10256.61</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5060-235-CM26</t>
+          <t>4322-263-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4916,27 +4916,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>765.04</v>
+        <v>13546.96</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5586-1359-CM26</t>
+          <t>4322-264-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4977,12 +4977,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5022,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>13682.38</v>
+        <v>3412.44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3518-171-CM26</t>
+          <t>3608-252-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5068,12 +5068,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5083,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8177.56</v>
+        <v>1589.94</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3486-247-CM26</t>
+          <t>722-43-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,22 +5104,22 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>15025.36</v>
+        <v>3342.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3151-282-CM26</t>
+          <t>4179-491-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>674.73</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>514848-425-CM26</t>
+          <t>5586-1311-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>4892.33</v>
+        <v>28915.22</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3151-284-CM26</t>
+          <t>5060-235-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,22 +5287,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,13 +5327,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>13747.14</v>
+        <v>765.04</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3151-285-CM26</t>
+          <t>5586-1359-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5388,13 +5388,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2337.21</v>
+        <v>13682.38</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3608-296-CM26</t>
+          <t>3518-171-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5419,12 +5419,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5434,12 +5434,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5449,13 +5449,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>7450.48</v>
+        <v>8177.56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3151-294-CM26</t>
+          <t>3486-247-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5510,13 +5510,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>3702.57</v>
+        <v>15025.36</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1028897-468-CM26</t>
+          <t>3151-282-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5526,27 +5526,27 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1116.7</v>
+        <v>674.73</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4406-460-CM26</t>
+          <t>514848-425-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5587,27 +5587,27 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5632,13 +5632,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10714.71</v>
+        <v>4892.33</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>765-128-CM26</t>
+          <t>3151-284-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5648,27 +5648,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5693,13 +5693,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2807.21</v>
+        <v>13747.14</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4179-616-CM26</t>
+          <t>3151-285-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5709,27 +5709,27 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>41910.02</v>
+        <v>2337.21</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5586-1682-CM26</t>
+          <t>3608-296-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5815,13 +5815,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>14361.93</v>
+        <v>7450.48</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>5586-1686-CM26</t>
+          <t>3151-294-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5861,12 +5861,12 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
@@ -5876,13 +5876,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>75654.55</v>
+        <v>3702.57</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4322-333-CM26</t>
+          <t>1028897-468-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5897,22 +5897,22 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5937,13 +5937,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2560.88</v>
+        <v>1116.7</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4112-64-CM26</t>
+          <t>4406-460-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5958,22 +5958,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE LUMACO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
@@ -5998,13 +5998,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3781.58</v>
+        <v>10714.71</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3151-376-CM26</t>
+          <t>4179-616-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,22 +6019,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,12 +6044,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
@@ -6059,13 +6059,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3269.62</v>
+        <v>41910.02</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3151-377-CM26</t>
+          <t>765-128-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,22 +6080,22 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7071.23</v>
+        <v>2807.21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4281-124-CM26</t>
+          <t>5586-1682-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>13580.85</v>
+        <v>14361.93</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1658-1552-CM26</t>
+          <t>5586-1686-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,22 +6202,22 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,13 +6242,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>9746.41</v>
+        <v>75654.55</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2547-155-CM26</t>
+          <t>4322-333-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>19781.6</v>
+        <v>2560.88</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3710-427-CM26</t>
+          <t>4112-64-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6319,27 +6319,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>6080.66</v>
+        <v>3781.58</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4323-145-CM26</t>
+          <t>3151-376-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>5566.42</v>
+        <v>3269.62</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5586-2295-CM26</t>
+          <t>3151-377-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>6409.22</v>
+        <v>7071.23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5586-2296-CM26</t>
+          <t>4281-124-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6502,12 +6502,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6532,12 +6532,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K100" t="inlineStr"/>
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>434.3</v>
+        <v>13580.85</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5586-2314-CM26</t>
+          <t>1658-1552-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6563,27 +6563,27 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1939.68</v>
+        <v>9746.41</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>4285-195-CM26</t>
+          <t>2547-155-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4183.61</v>
+        <v>19781.6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>765-153-CM26</t>
+          <t>3710-427-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,22 +6690,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1472.03</v>
+        <v>6080.66</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3808-155-CM26</t>
+          <t>5586-2296-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,13 +6791,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2070.6</v>
+        <v>434.3</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3494-225-CM26</t>
+          <t>4323-145-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,22 +6812,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K105" t="inlineStr"/>
@@ -6852,13 +6852,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>28584.81</v>
+        <v>5566.42</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3752-183-CM26</t>
+          <t>5586-2295-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
@@ -6913,13 +6913,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1017.39</v>
+        <v>6409.22</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>5060-451-CM26</t>
+          <t>4285-195-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6934,7 +6934,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,12 +6959,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3810.86</v>
+        <v>4183.61</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>722-94-CM26</t>
+          <t>5586-2314-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1472.03</v>
+        <v>1939.68</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3836-496-CM26</t>
+          <t>765-153-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7056,22 +7056,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>27563.23</v>
+        <v>1472.03</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>5060-460-CM26</t>
+          <t>3808-155-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7127,12 +7127,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>6890.81</v>
+        <v>2070.6</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>4114-199-CM26</t>
+          <t>3494-225-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7178,22 +7178,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>32238.71</v>
+        <v>28584.81</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>4114-201-CM26</t>
+          <t>3752-183-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>737.8</v>
+        <v>1017.39</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3809-98-CM26</t>
+          <t>5060-451-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,13 +7340,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>707.34</v>
+        <v>3810.86</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3494-235-CM26</t>
+          <t>722-94-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7361,22 +7361,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K114" t="inlineStr"/>
@@ -7401,13 +7401,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6538.24</v>
+        <v>1472.03</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4179-888-CM26</t>
+          <t>3836-496-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7432,12 +7432,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE TOLTEN</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1910.99</v>
+        <v>27563.23</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4179-889-CM26</t>
+          <t>5060-460-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,13 +7523,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>736.37</v>
+        <v>6890.81</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>5586-2584-CM26</t>
+          <t>4114-199-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7554,12 +7554,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7584,6 +7584,372 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
+        <v>32238.71</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>4114-201-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>69.181.000-3</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>737.8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3809-98-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>69.180.200-0</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUREN</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>77.108.316-1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>707.34</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>4179-888-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>69.190.100-9</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>1910.99</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>4179-889-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>69.190.100-9</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>736.37</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>3494-235-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>69.190.800-3</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>6538.24</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>5586-2584-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
         <v>10193.3</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M222"/>
+  <dimension ref="A1:M236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1612,7 +1612,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>4281-48-CM25</t>
+          <t>4281-47-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3683.05</v>
+        <v>3968.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4281-47-CM25</t>
+          <t>4281-48-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3968.59</v>
+        <v>3683.05</v>
       </c>
     </row>
     <row r="22">
@@ -2710,7 +2710,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3486-305-CM25</t>
+          <t>1658-2874-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5476.38</v>
+        <v>22328.57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1658-2874-CM25</t>
+          <t>3486-305-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,12 +2796,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>22328.57</v>
+        <v>5476.38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1028897-645-CM25</t>
+          <t>722-90-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,17 +2852,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>14618.2</v>
+        <v>14872.62</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>722-90-CM25</t>
+          <t>1028897-645-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,17 +2913,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2933,12 +2933,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>14872.62</v>
+        <v>14618.2</v>
       </c>
     </row>
     <row r="42">
@@ -4052,7 +4052,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4322-356-CM25</t>
+          <t>3710-580-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4072,17 +4072,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>26643.92</v>
+        <v>51223.55</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3710-580-CM25</t>
+          <t>4322-356-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4133,17 +4133,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,12 +4153,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>51223.55</v>
+        <v>26643.92</v>
       </c>
     </row>
     <row r="62">
@@ -4357,7 +4357,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4177-103-CM25</t>
+          <t>2387-353-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4412,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>9535.35</v>
+        <v>5951.79</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2387-353-CM25</t>
+          <t>4177-103-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5951.79</v>
+        <v>9535.35</v>
       </c>
     </row>
     <row r="67">
@@ -4540,7 +4540,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1658-3898-CM25</t>
+          <t>3933-87-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>27049.83</v>
+        <v>13186.62</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3933-87-CM25</t>
+          <t>1658-3898-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>13186.62</v>
+        <v>27049.83</v>
       </c>
     </row>
     <row r="70">
@@ -4906,7 +4906,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2547-332-CM25</t>
+          <t>5586-2766-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4931,12 +4931,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -4961,13 +4961,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5330.72</v>
+        <v>5233.62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5586-2766-CM25</t>
+          <t>2547-332-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5233.62</v>
+        <v>5330.72</v>
       </c>
     </row>
     <row r="76">
@@ -6248,7 +6248,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2389-727-CM25</t>
+          <t>3887-523-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>9480.49</v>
+        <v>2387.14</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3887-523-CM25</t>
+          <t>2389-727-CM25</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>2387.14</v>
+        <v>9480.49</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1658-5413-CM25</t>
+          <t>2388-398-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,13 +6425,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2544.7</v>
+        <v>10124.52</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2388-397-CM25</t>
+          <t>1658-5413-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
@@ -6486,13 +6486,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>13132.25</v>
+        <v>2544.7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2388-398-CM25</t>
+          <t>2388-399-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6547,13 +6547,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>10124.52</v>
+        <v>5062.26</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2388-399-CM25</t>
+          <t>2388-397-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>5062.26</v>
+        <v>13132.25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>986278-2017-CM25</t>
+          <t>3933-137-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6634,17 +6634,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>65.148.017-5</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>3318.49</v>
+        <v>6924.35</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3933-137-CM25</t>
+          <t>986278-2016-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6695,17 +6695,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6730,13 +6730,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>6924.35</v>
+        <v>2677.5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>986278-2016-CM25</t>
+          <t>986278-2017-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2677.5</v>
+        <v>3318.49</v>
       </c>
     </row>
     <row r="105">
@@ -6980,7 +6980,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5586-4059-CM25</t>
+          <t>5586-4058-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>23526</v>
+        <v>17164.56</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5586-4058-CM25</t>
+          <t>5586-4059-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>17164.56</v>
+        <v>23526</v>
       </c>
     </row>
     <row r="110">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">AURA XD SPA </t>
+          <t>AURA XD SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -7407,7 +7407,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4285-342-CM25</t>
+          <t>4179-2403-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7427,17 +7427,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K115" t="inlineStr"/>
@@ -7462,13 +7462,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3237.23</v>
+        <v>784.2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>4179-2403-CM25</t>
+          <t>4285-342-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7488,17 +7488,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7508,12 +7508,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K116" t="inlineStr"/>
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>784.2</v>
+        <v>3237.23</v>
       </c>
     </row>
     <row r="117">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9237,7 +9237,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>722-28-CM26</t>
+          <t>1075337-7387-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9262,12 +9262,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K145" t="inlineStr"/>
@@ -9292,13 +9292,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>12762.75</v>
+        <v>428.4</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>4179-315-CM26</t>
+          <t>722-28-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9338,12 +9338,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K146" t="inlineStr"/>
@@ -9353,13 +9353,13 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>660.45</v>
+        <v>12762.75</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>3485-262-CM26</t>
+          <t>4179-315-CM26</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9374,22 +9374,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9399,12 +9399,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K147" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>10682.75</v>
+        <v>660.45</v>
       </c>
     </row>
     <row r="148">
@@ -9542,7 +9542,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3922-238-CM26</t>
+          <t>3485-262-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9597,13 +9597,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3102.29</v>
+        <v>10682.75</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1658-724-CM26</t>
+          <t>3922-238-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9643,12 +9643,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9658,13 +9658,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>19010.25</v>
+        <v>3102.29</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1028897-246-CM26</t>
+          <t>1658-724-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9679,22 +9679,22 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9719,13 +9719,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>14921.53</v>
+        <v>19010.25</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>5586-907-CM26</t>
+          <t>1028897-246-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9740,22 +9740,22 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K153" t="inlineStr"/>
@@ -9780,13 +9780,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>971.85</v>
+        <v>14921.53</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>3708-141-CM26</t>
+          <t>5586-907-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9826,12 +9826,12 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K154" t="inlineStr"/>
@@ -9841,13 +9841,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>14389.77</v>
+        <v>971.85</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3751-101-CM26</t>
+          <t>3708-141-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9887,12 +9887,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K155" t="inlineStr"/>
@@ -9902,13 +9902,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>8701.049999999999</v>
+        <v>14389.77</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3705-180-CM26</t>
+          <t>3751-101-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -9928,17 +9928,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K156" t="inlineStr"/>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>10256.61</v>
+        <v>8701.049999999999</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4322-264-CM26</t>
+          <t>3705-180-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K157" t="inlineStr"/>
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>3412.44</v>
+        <v>10256.61</v>
       </c>
     </row>
     <row r="158">
@@ -10091,7 +10091,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>722-43-CM26</t>
+          <t>4322-264-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10101,27 +10101,27 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10146,13 +10146,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3342.12</v>
+        <v>3412.44</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>3608-252-CM26</t>
+          <t>722-43-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10172,17 +10172,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10207,13 +10207,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1589.94</v>
+        <v>3342.12</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>4179-491-CM26</t>
+          <t>3608-252-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10228,22 +10228,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10253,12 +10253,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10268,13 +10268,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>96.39</v>
+        <v>1589.94</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5586-1311-CM26</t>
+          <t>4179-491-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10289,22 +10289,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10329,13 +10329,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>28915.22</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>5060-235-CM26</t>
+          <t>5586-1311-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10350,22 +10350,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10390,13 +10390,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>765.04</v>
+        <v>28915.22</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5586-1359-CM26</t>
+          <t>5060-235-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10416,17 +10416,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K164" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>13682.38</v>
+        <v>765.04</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3518-171-CM26</t>
+          <t>5586-1359-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10482,12 +10482,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10497,12 +10497,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10512,13 +10512,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>8177.56</v>
+        <v>13682.38</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>3486-247-CM26</t>
+          <t>3518-171-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10533,7 +10533,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10558,12 +10558,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>15025.36</v>
+        <v>8177.56</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>3151-282-CM26</t>
+          <t>3486-247-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10604,12 +10604,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10619,12 +10619,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10634,13 +10634,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>674.73</v>
+        <v>15025.36</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>514848-425-CM26</t>
+          <t>3151-282-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10655,22 +10655,22 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10680,12 +10680,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -10695,13 +10695,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4892.33</v>
+        <v>674.73</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3151-284-CM26</t>
+          <t>514848-425-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10721,17 +10721,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K169" t="inlineStr"/>
@@ -10756,13 +10756,13 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>13747.14</v>
+        <v>4892.33</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3151-285-CM26</t>
+          <t>3151-284-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2337.21</v>
+        <v>13747.14</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3608-296-CM26</t>
+          <t>3151-285-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10848,12 +10848,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K171" t="inlineStr"/>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>7450.48</v>
+        <v>2337.21</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3151-294-CM26</t>
+          <t>3608-296-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K172" t="inlineStr"/>
@@ -10939,13 +10939,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3702.57</v>
+        <v>7450.48</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1028897-468-CM26</t>
+          <t>3151-294-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10955,27 +10955,27 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K173" t="inlineStr"/>
@@ -11000,13 +11000,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>1116.7</v>
+        <v>3702.57</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4406-460-CM26</t>
+          <t>1028897-468-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11021,22 +11021,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>65.154.272-3</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11061,13 +11061,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>10714.71</v>
+        <v>1116.7</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4179-616-CM26</t>
+          <t>4406-460-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11107,12 +11107,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>41910.02</v>
+        <v>10714.71</v>
       </c>
     </row>
     <row r="176">
@@ -11189,7 +11189,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>5586-1682-CM26</t>
+          <t>4179-616-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11204,22 +11204,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -11229,12 +11229,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K177" t="inlineStr"/>
@@ -11244,13 +11244,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>14361.93</v>
+        <v>41910.02</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>5586-1686-CM26</t>
+          <t>5586-1682-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -11290,12 +11290,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11305,13 +11305,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>75654.55</v>
+        <v>14361.93</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>4322-333-CM26</t>
+          <t>5586-1686-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11366,13 +11366,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>2560.88</v>
+        <v>75654.55</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4112-64-CM26</t>
+          <t>4322-333-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11387,22 +11387,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K180" t="inlineStr"/>
@@ -11427,13 +11427,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3781.58</v>
+        <v>2560.88</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>3151-376-CM26</t>
+          <t>4112-64-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11448,22 +11448,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11488,13 +11488,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>3269.62</v>
+        <v>3781.58</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3151-377-CM26</t>
+          <t>3151-376-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11549,13 +11549,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7071.23</v>
+        <v>3269.62</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>4281-124-CM26</t>
+          <t>3151-377-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -11580,12 +11580,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K183" t="inlineStr"/>
@@ -11610,13 +11610,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>13580.85</v>
+        <v>7071.23</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2547-155-CM26</t>
+          <t>4281-124-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11641,12 +11641,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>19781.6</v>
+        <v>13580.85</v>
       </c>
     </row>
     <row r="185">
@@ -11738,7 +11738,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>3710-427-CM26</t>
+          <t>2547-155-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11748,12 +11748,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11793,13 +11793,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6080.66</v>
+        <v>19781.6</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>4323-145-CM26</t>
+          <t>3710-427-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11814,22 +11814,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11854,13 +11854,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>5566.42</v>
+        <v>6080.66</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5586-2295-CM26</t>
+          <t>1075337-8928-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11875,22 +11875,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11915,13 +11915,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>6409.22</v>
+        <v>733.04</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>5586-2296-CM26</t>
+          <t>4323-145-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11941,17 +11941,17 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11976,13 +11976,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>434.3</v>
+        <v>5566.42</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5586-2314-CM26</t>
+          <t>5586-2295-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -12037,13 +12037,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1939.68</v>
+        <v>6409.22</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>4285-195-CM26</t>
+          <t>5586-2296-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12098,13 +12098,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>4183.61</v>
+        <v>434.3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>765-153-CM26</t>
+          <t>4285-195-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12119,22 +12119,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12159,13 +12159,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1472.03</v>
+        <v>4183.61</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3752-183-CM26</t>
+          <t>5586-2314-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K193" t="inlineStr"/>
@@ -12220,13 +12220,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1017.39</v>
+        <v>1939.68</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>3494-225-CM26</t>
+          <t>765-153-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K194" t="inlineStr"/>
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>28584.81</v>
+        <v>1472.03</v>
       </c>
     </row>
     <row r="195">
@@ -12348,7 +12348,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>5060-451-CM26</t>
+          <t>3494-225-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12363,22 +12363,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K196" t="inlineStr"/>
@@ -12403,13 +12403,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>3810.86</v>
+        <v>28584.81</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>722-94-CM26</t>
+          <t>3752-183-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12424,7 +12424,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K197" t="inlineStr"/>
@@ -12464,13 +12464,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1472.03</v>
+        <v>1017.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3836-496-CM26</t>
+          <t>5060-451-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12485,22 +12485,22 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.191.400-3</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -12510,12 +12510,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -12525,13 +12525,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>27563.23</v>
+        <v>3810.86</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>5060-460-CM26</t>
+          <t>722-94-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -12556,12 +12556,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -12586,13 +12586,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>6890.81</v>
+        <v>1472.03</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4114-199-CM26</t>
+          <t>3836-496-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.191.400-3</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K200" t="inlineStr"/>
@@ -12647,13 +12647,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>32238.71</v>
+        <v>27563.23</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>4114-201-CM26</t>
+          <t>5060-460-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -12678,12 +12678,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12693,12 +12693,12 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K201" t="inlineStr"/>
@@ -12708,13 +12708,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>737.8</v>
+        <v>6890.81</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>3809-98-CM26</t>
+          <t>4114-199-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K202" t="inlineStr"/>
@@ -12769,13 +12769,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>707.34</v>
+        <v>32238.71</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4179-889-CM26</t>
+          <t>4114-201-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -12800,12 +12800,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -12815,12 +12815,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K203" t="inlineStr"/>
@@ -12830,13 +12830,13 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>736.37</v>
+        <v>737.8</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3494-235-CM26</t>
+          <t>3809-98-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12851,22 +12851,22 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K204" t="inlineStr"/>
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>6538.24</v>
+        <v>707.34</v>
       </c>
     </row>
     <row r="205">
@@ -12917,7 +12917,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -12958,7 +12958,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4406-655-CM26</t>
+          <t>4179-889-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12968,27 +12968,27 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Lumaco</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K206" t="inlineStr"/>
@@ -13013,13 +13013,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>815.59</v>
+        <v>736.37</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3887-274-CM26</t>
+          <t>3494-235-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13029,27 +13029,27 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13059,12 +13059,12 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K207" t="inlineStr"/>
@@ -13074,13 +13074,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>102.33</v>
+        <v>6538.24</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>4406-665-CM26</t>
+          <t>4406-655-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13095,7 +13095,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -13135,13 +13135,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>3262.36</v>
+        <v>815.59</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>5061-453-CM26</t>
+          <t>3887-274-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -13166,12 +13166,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13181,12 +13181,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13196,13 +13196,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2853.92</v>
+        <v>102.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>960855-21-CM26</t>
+          <t>4406-665-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13217,22 +13217,22 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.180.500-K</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13242,12 +13242,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13257,13 +13257,13 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2776.15</v>
+        <v>3262.36</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>3922-718-CM26</t>
+          <t>5061-453-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -13288,12 +13288,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -13303,12 +13303,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K211" t="inlineStr"/>
@@ -13318,13 +13318,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>816.71</v>
+        <v>2853.92</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3922-719-CM26</t>
+          <t>960855-21-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13344,17 +13344,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13364,12 +13364,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13379,13 +13379,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2475.2</v>
+        <v>2776.15</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>5586-2584-CM26</t>
+          <t>3922-718-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13400,7 +13400,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13410,12 +13410,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>10193.3</v>
+        <v>816.71</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>4176-311-CM26</t>
+          <t>3922-719-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13486,12 +13486,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -13501,13 +13501,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>4884.47</v>
+        <v>2475.2</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>5586-2620-CM26</t>
+          <t>5586-2584-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13522,7 +13522,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -13547,12 +13547,12 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>6197.4</v>
+        <v>10193.3</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>3428-230-CM26</t>
+          <t>4176-311-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13583,22 +13583,22 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -13623,13 +13623,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>7011.48</v>
+        <v>4884.47</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>3486-425-CM26</t>
+          <t>5586-2620-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13644,7 +13644,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -13654,12 +13654,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -13669,12 +13669,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -13684,13 +13684,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>10142.25</v>
+        <v>6197.4</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>3933-80-CM26</t>
+          <t>3428-230-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13705,22 +13705,22 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13745,13 +13745,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>6775.86</v>
+        <v>7011.48</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>5586-2896-CM26</t>
+          <t>3486-425-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K219" t="inlineStr"/>
@@ -13806,13 +13806,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>4284</v>
+        <v>10142.25</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>3742-181-CM26</t>
+          <t>3933-80-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13827,7 +13827,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -13837,12 +13837,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K220" t="inlineStr"/>
@@ -13867,13 +13867,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>5934.71</v>
+        <v>6775.86</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1075337-9533-CM26</t>
+          <t>3742-181-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -13898,12 +13898,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13913,12 +13913,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>RICOH</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>96.513.980-k</t>
+          <t>76.179.170-2</t>
         </is>
       </c>
       <c r="K221" t="inlineStr"/>
@@ -13928,13 +13928,13 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>279.64</v>
+        <v>5934.71</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1028897-1066-CM26</t>
+          <t>5586-2896-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13949,22 +13949,22 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>65.154.272-3</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -13974,12 +13974,12 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K222" t="inlineStr"/>
@@ -13989,7 +13989,861 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>1075337-9533-CM26</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>61.602.222-9</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>279.64</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>1028897-1066-CM26</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>65.154.272-3</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACION COSTA ARAUCANIA</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="n">
         <v>6829.41</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>3933-81-CM26</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="n">
+        <v>3387.93</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>514848-962-CM26</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>69.190.100-9</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>AURA XD SPA</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>76.359.312-6</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="n">
+        <v>32506.67</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>1078177-826-CM26</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>60.505.522-2</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="n">
+        <v>1520.82</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>3518-373-CM26</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>69.180.700-2</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="n">
+        <v>1868.18</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>765-189-CM26</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>72.396.000-2</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="n">
+        <v>6717.5</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>3710-622-CM26</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>69.180.900-5</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>I.I.A. Ltda.</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="n">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>1510-406-CM26</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>60.511.091-6</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE MALLECO</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>5586-3200-CM26</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="n">
+        <v>19831.68</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>5586-3220-CM26</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>AURA XD SPA</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>76.359.312-6</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="n">
+        <v>8616.27</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>1589-75-CM26</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>60.511.090-8</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE LA ARAUCANÍA</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>5061-661-CM26</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>BOOKCOMPUTER</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="n">
+        <v>1705.92</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>5586-3394-CM26</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>87.912.900-1</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>FRANCO</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="n">
+        <v>2903.6</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
@@ -562,7 +562,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1598,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1980,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2301,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2366,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2431,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2496,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2561,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2626,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2691,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2756,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2821,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2886,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2951,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3016,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3081,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3146,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3211,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3276,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3341,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3467,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3532,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3597,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3723,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3849,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3914,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3979,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4044,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4231,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4296,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4361,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4487,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4552,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4678,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4743,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4808,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4873,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4938,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5003,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5068,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5133,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5198,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5263,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5328,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5393,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5519,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5584,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5771,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5897,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5962,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6027,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6214,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6279,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6405,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6531,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6657,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6722,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6787,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6852,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6917,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6982,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7047,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7112,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7177,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7242,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7307,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7433,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7559,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7624,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7750,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7815,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7880,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7945,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8071,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8136,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8262,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8327,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8392,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8579,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8644,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8709,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8835,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8900,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8965,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9091,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9278,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9343,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9591,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9656,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9721,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9786,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9912,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9977,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10042,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10229,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10294,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10359,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10424,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10794,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10859,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10924,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +10989,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11176,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11241,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11489,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11615,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11741,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11806,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11871,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12180,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12245,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12310,11 @@
           <t>77.508.642-4</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12375,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12440,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12505,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12631,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12696,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12883,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12948,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13013,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13200,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13265,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13330,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13456,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13521,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13586,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13651,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13716,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13842,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13907,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14033,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14159,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14224,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14289,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14354,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14480,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14667,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +14793,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15041,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15167,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15232,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15358,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15423,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M236"/>
+  <dimension ref="A1:M239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1359,7 +1359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3611-106-CM25</t>
+          <t>2387-165-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1399,17 +1399,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>3064.19</v>
+        <v>7100.73</v>
       </c>
     </row>
     <row r="16">
@@ -1485,7 +1485,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2387-165-CM25</t>
+          <t>3611-106-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1510,12 +1510,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1525,17 +1525,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>7100.73</v>
+        <v>3064.19</v>
       </c>
     </row>
     <row r="18">
@@ -2318,7 +2318,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1028897-463-CM25</t>
+          <t>1028897-464-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2441.67</v>
+        <v>3888.16</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1028897-464-CM25</t>
+          <t>1028897-463-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3888.16</v>
+        <v>2441.67</v>
       </c>
     </row>
     <row r="32">
@@ -3358,7 +3358,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4406-411-CM25</t>
+          <t>4406-412-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3398,28 +3398,32 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>3240.7</v>
+        <v>3727.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4406-412-CM25</t>
+          <t>4406-411-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3459,26 +3463,22 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3727.08</v>
+        <v>3240.7</v>
       </c>
     </row>
     <row r="48">
@@ -3801,7 +3801,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4112-145-CM25</t>
+          <t>5586-1991-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.181.000-3</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3841,17 +3841,17 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>17057.46</v>
+        <v>13719.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5586-1991-CM25</t>
+          <t>4112-145-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3886,17 +3886,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.181.000-3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3925,7 +3925,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>13719.36</v>
+        <v>17057.46</v>
       </c>
     </row>
     <row r="55">
@@ -4122,7 +4122,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1658-3230-CM25</t>
+          <t>4285-144-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4162,28 +4162,32 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>44904.58</v>
+        <v>7013.76</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>4285-144-CM25</t>
+          <t>1658-3230-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4208,12 +4212,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4223,32 +4227,28 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>7013.76</v>
+        <v>44904.58</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3710-580-CM25</t>
+          <t>4322-356-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.190.300-1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE PERQUENCO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4288,17 +4288,17 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4307,13 +4307,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>51223.55</v>
+        <v>26643.92</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4322-356-CM25</t>
+          <t>3710-580-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4333,17 +4333,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.190.300-1</t>
+          <t>69.180.900-5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERQUENCO</t>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4353,17 +4353,17 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4372,7 +4372,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>26643.92</v>
+        <v>51223.55</v>
       </c>
     </row>
     <row r="62">
@@ -4569,7 +4569,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2387-353-CM25</t>
+          <t>4177-103-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4589,17 +4589,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4609,28 +4609,32 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>5951.79</v>
+        <v>9535.35</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4177-103-CM25</t>
+          <t>2387-353-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4650,17 +4654,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4670,26 +4674,22 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>9535.35</v>
+        <v>5951.79</v>
       </c>
     </row>
     <row r="67">
@@ -4760,7 +4760,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3933-87-CM25</t>
+          <t>1658-3898-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4800,12 +4800,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>13186.62</v>
+        <v>27049.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1658-3898-CM25</t>
+          <t>3933-87-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4865,12 +4865,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -4884,7 +4884,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>27049.83</v>
+        <v>13186.62</v>
       </c>
     </row>
     <row r="70">
@@ -5150,7 +5150,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5586-2766-CM25</t>
+          <t>2547-332-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -5209,13 +5209,13 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5233.62</v>
+        <v>5330.72</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2547-332-CM25</t>
+          <t>5586-2766-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -5274,13 +5274,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5330.72</v>
+        <v>5233.62</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3495-191-CM25</t>
+          <t>514847-1227-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5300,17 +5300,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7306.6</v>
+        <v>16271.92</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>514847-1227-CM25</t>
+          <t>3495-191-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5365,17 +5365,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>16271.92</v>
+        <v>7306.6</v>
       </c>
     </row>
     <row r="78">
@@ -6105,7 +6105,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4114-306-CM25</t>
+          <t>4114-307-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6145,28 +6145,32 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOTABLET SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.292.976-7</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>3498.6</v>
+        <v>3486.46</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4114-307-CM25</t>
+          <t>4114-306-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6206,26 +6210,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TODOTABLET SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.292.976-7</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>3486.46</v>
+        <v>3498.6</v>
       </c>
     </row>
     <row r="91">
@@ -6739,7 +6739,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1658-5413-CM25</t>
+          <t>2388-399-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6764,12 +6764,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.191.600-6</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE PUCON</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6798,13 +6798,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2544.7</v>
+        <v>5062.26</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2388-399-CM25</t>
+          <t>2388-397-CM25</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -6863,13 +6863,13 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>5062.26</v>
+        <v>13132.25</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2388-397-CM25</t>
+          <t>1658-5413-CM25</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.191.600-6</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCON</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -6928,13 +6928,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>13132.25</v>
+        <v>2544.7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3933-137-CM25</t>
+          <t>986278-2017-CM25</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6954,17 +6954,17 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>65.148.017-5</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6974,12 +6974,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>COMPUTACION E INGENIERIA S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.693.120-5</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -6993,7 +6993,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>6924.35</v>
+        <v>3318.49</v>
       </c>
     </row>
     <row r="103">
@@ -7064,7 +7064,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>986278-2017-CM25</t>
+          <t>3933-137-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7084,17 +7084,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>65.148.017-5</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>COMPUTACION E INGENIERIA S A</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.693.120-5</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7123,13 +7123,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>3318.49</v>
+        <v>6924.35</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3933-138-CM25</t>
+          <t>3933-139-CM25</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7169,17 +7169,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7188,13 +7188,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>5035.89</v>
+        <v>9267.719999999999</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3933-139-CM25</t>
+          <t>3933-138-CM25</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7234,17 +7234,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>9267.719999999999</v>
+        <v>5035.89</v>
       </c>
     </row>
     <row r="107">
@@ -7324,7 +7324,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>5586-4058-CM25</t>
+          <t>5586-4059-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7364,28 +7364,32 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>17164.56</v>
+        <v>23526</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>5586-4059-CM25</t>
+          <t>5586-4058-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7425,26 +7429,22 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>23526</v>
+        <v>17164.56</v>
       </c>
     </row>
     <row r="110">
@@ -8088,7 +8088,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>3477-75-CM26</t>
+          <t>4179-61-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -8128,17 +8128,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>22700.92</v>
+        <v>1239.92</v>
       </c>
     </row>
     <row r="121">
@@ -8214,7 +8214,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>4179-61-CM26</t>
+          <t>3477-75-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8254,17 +8254,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1239.92</v>
+        <v>22700.92</v>
       </c>
     </row>
     <row r="123">
@@ -9929,7 +9929,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3212-43-CM26</t>
+          <t>3485-262-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9949,17 +9949,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>69.180.500-k</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.977.985-K</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -9988,13 +9988,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>1877.82</v>
+        <v>10682.75</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>3485-262-CM26</t>
+          <t>3212-43-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10014,17 +10014,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>10682.75</v>
+        <v>1877.82</v>
       </c>
     </row>
     <row r="151">
@@ -10876,7 +10876,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>5060-235-CM26</t>
+          <t>5586-1359-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10896,17 +10896,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10935,13 +10935,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>765.04</v>
+        <v>13682.38</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>5586-1359-CM26</t>
+          <t>5060-235-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10961,17 +10961,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10981,17 +10981,17 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>13682.38</v>
+        <v>765.04</v>
       </c>
     </row>
     <row r="166">
@@ -11193,7 +11193,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>514848-425-CM26</t>
+          <t>3151-285-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11213,17 +11213,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11233,32 +11233,28 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>4892.33</v>
+        <v>2337.21</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3151-284-CM26</t>
+          <t>514848-425-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11278,17 +11274,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11298,28 +11294,32 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>13747.14</v>
+        <v>4892.33</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3151-285-CM26</t>
+          <t>3151-284-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>2337.21</v>
+        <v>13747.14</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3608-296-CM26</t>
+          <t>3151-294-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11420,28 +11420,32 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>7450.48</v>
+        <v>3702.57</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3151-294-CM26</t>
+          <t>3608-296-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11466,12 +11470,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11481,26 +11485,22 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3702.57</v>
+        <v>7450.48</v>
       </c>
     </row>
     <row r="174">
@@ -12010,7 +12010,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3151-376-CM26</t>
+          <t>3151-377-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12065,13 +12065,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3269.62</v>
+        <v>7071.23</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3151-377-CM26</t>
+          <t>3151-376-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>7071.23</v>
+        <v>3269.62</v>
       </c>
     </row>
     <row r="184">
@@ -12522,7 +12522,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5586-2295-CM26</t>
+          <t>5586-2296-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12562,28 +12562,32 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>6409.22</v>
+        <v>434.3</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5586-2296-CM26</t>
+          <t>5586-2295-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12623,32 +12627,28 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>434.3</v>
+        <v>6409.22</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4285-195-CM26</t>
+          <t>5586-2314-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12688,32 +12688,28 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>4183.61</v>
+        <v>1939.68</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>5586-2314-CM26</t>
+          <t>4285-195-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12738,12 +12734,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12753,22 +12749,26 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1939.68</v>
+        <v>4183.61</v>
       </c>
     </row>
     <row r="194">
@@ -12835,7 +12835,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3808-155-CM26</t>
+          <t>3752-183-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12875,12 +12875,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>2070.6</v>
+        <v>1017.39</v>
       </c>
     </row>
     <row r="196">
@@ -12965,7 +12965,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3752-183-CM26</t>
+          <t>3808-155-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13024,7 +13024,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1017.39</v>
+        <v>2070.6</v>
       </c>
     </row>
     <row r="198">
@@ -13473,7 +13473,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4179-888-CM26</t>
+          <t>4179-889-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13532,13 +13532,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1910.99</v>
+        <v>736.37</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>4179-889-CM26</t>
+          <t>3494-235-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13578,17 +13578,17 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13597,13 +13597,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>736.37</v>
+        <v>6538.24</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>3494-235-CM26</t>
+          <t>4179-888-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13643,17 +13643,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -13662,7 +13662,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>6538.24</v>
+        <v>1910.99</v>
       </c>
     </row>
     <row r="208">
@@ -13733,7 +13733,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>3887-274-CM26</t>
+          <t>4406-665-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13773,28 +13773,32 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>102.33</v>
+        <v>3262.36</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>4406-665-CM26</t>
+          <t>3887-274-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13819,12 +13823,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Lumaco</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13834,26 +13838,22 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3262.36</v>
+        <v>102.33</v>
       </c>
     </row>
     <row r="211">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -15375,7 +15375,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>5061-661-CM26</t>
+          <t>5586-3394-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15390,7 +15390,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -15400,12 +15400,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15415,32 +15415,28 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1705.92</v>
+        <v>2903.6</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>5586-3394-CM26</t>
+          <t>969221-18-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15450,12 +15446,12 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>oct-2026</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -15465,12 +15461,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15480,22 +15476,217 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K236" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>2903.6</v>
+        <v>6886.85</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>3200-399-CM26</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>69.191.100-4</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="n">
+        <v>56870.1</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2736-418-CM26</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>69.180.100-4</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ALCA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>76.596.570-5</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="n">
+        <v>27149.53</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>4115-154-CM26</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>69.181.000-3</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURACAUTIN</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="n">
+        <v>7034.93</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
@@ -13237,7 +13237,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -13879,7 +13879,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M239"/>
+  <dimension ref="A1:M240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9295,7 +9295,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1658-739-CM26</t>
+          <t>765-81-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9320,12 +9320,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9335,32 +9335,28 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>6640.06</v>
+        <v>68338.73</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>765-81-CM26</t>
+          <t>3922-178-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9380,17 +9376,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9400,12 +9396,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K140" t="inlineStr"/>
@@ -9415,13 +9411,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>68338.73</v>
+        <v>685.4400000000001</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>3922-178-CM26</t>
+          <t>1658-739-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9441,17 +9437,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9461,22 +9457,26 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr"/>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>685.4400000000001</v>
+        <v>6640.06</v>
       </c>
     </row>
     <row r="142">
@@ -9673,7 +9673,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1075337-7387-CM26</t>
+          <t>722-28-CM26</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9713,12 +9713,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -9732,13 +9732,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>428.4</v>
+        <v>12762.75</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>722-28-CM26</t>
+          <t>1075337-7387-CM26</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9778,12 +9778,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -9797,7 +9797,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>12762.75</v>
+        <v>428.4</v>
       </c>
     </row>
     <row r="147">
@@ -10376,7 +10376,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>3751-101-CM26</t>
+          <t>3705-180-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10396,17 +10396,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -10416,32 +10416,28 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.683.370-3</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>8701.049999999999</v>
+        <v>10256.61</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>3705-180-CM26</t>
+          <t>3751-101-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10461,17 +10457,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10481,28 +10477,32 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>ESPEX INGENIERIA LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>77.683.370-3</t>
-        </is>
-      </c>
-      <c r="K157" t="inlineStr"/>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>10256.61</v>
+        <v>8701.049999999999</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4322-263-CM26</t>
+          <t>4322-264-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10542,12 +10542,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K158" t="inlineStr"/>
@@ -10557,13 +10557,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>13546.96</v>
+        <v>3412.44</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>4322-264-CM26</t>
+          <t>4322-263-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10618,13 +10618,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>3412.44</v>
+        <v>13546.96</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>722-43-CM26</t>
+          <t>3608-252-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA IGESCOM SPA</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.152.668-3</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10679,13 +10679,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>3342.12</v>
+        <v>1589.94</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>3608-252-CM26</t>
+          <t>722-43-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10705,17 +10705,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10725,12 +10725,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA IGESCOM SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.152.668-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10740,7 +10740,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1589.94</v>
+        <v>3342.12</v>
       </c>
     </row>
     <row r="162">
@@ -11193,7 +11193,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3151-285-CM26</t>
+          <t>3151-284-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>2337.21</v>
+        <v>13747.14</v>
       </c>
     </row>
     <row r="170">
@@ -11319,7 +11319,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3151-284-CM26</t>
+          <t>3151-285-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11374,13 +11374,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>13747.14</v>
+        <v>2337.21</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>3151-294-CM26</t>
+          <t>3608-296-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>69.191.100-4</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LONCOCHE</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11420,32 +11420,28 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
-        </is>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3702.57</v>
+        <v>7450.48</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>3608-296-CM26</t>
+          <t>3151-294-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11470,12 +11466,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.191.100-4</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>I MUNICIPALIDAD DE LONCOCHE</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11485,22 +11481,26 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>7450.48</v>
+        <v>3702.57</v>
       </c>
     </row>
     <row r="174">
@@ -12010,7 +12010,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>3151-377-CM26</t>
+          <t>3151-376-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12065,13 +12065,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7071.23</v>
+        <v>3269.62</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>3151-376-CM26</t>
+          <t>3151-377-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12126,7 +12126,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3269.62</v>
+        <v>7071.23</v>
       </c>
     </row>
     <row r="184">
@@ -12522,7 +12522,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>5586-2296-CM26</t>
+          <t>5586-2295-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12562,32 +12562,28 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>434.3</v>
+        <v>6409.22</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>5586-2295-CM26</t>
+          <t>5586-2296-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12627,28 +12623,32 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>6409.22</v>
+        <v>434.3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>5586-2314-CM26</t>
+          <t>4285-195-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12673,12 +12673,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>87.912.900-1</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA FRONTERA</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12688,28 +12688,32 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K192" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>1939.68</v>
+        <v>4183.61</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>4285-195-CM26</t>
+          <t>5586-2314-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12734,12 +12738,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>69.191.000-8</t>
+          <t>87.912.900-1</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CUNCO</t>
+          <t>UNIVERSIDAD DE LA FRONTERA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12749,26 +12753,22 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>4183.61</v>
+        <v>1939.68</v>
       </c>
     </row>
     <row r="194">
@@ -12835,7 +12835,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>3752-183-CM26</t>
+          <t>3808-155-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12860,12 +12860,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -12875,12 +12875,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
@@ -12894,7 +12894,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1017.39</v>
+        <v>2070.6</v>
       </c>
     </row>
     <row r="196">
@@ -12965,7 +12965,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3808-155-CM26</t>
+          <t>3752-183-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12990,12 +12990,12 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13005,12 +13005,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -13024,13 +13024,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>2070.6</v>
+        <v>1017.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5060-451-CM26</t>
+          <t>722-94-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13050,17 +13050,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>72.201.100-7</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K198" t="inlineStr"/>
@@ -13085,13 +13085,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3810.86</v>
+        <v>1472.03</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>722-94-CM26</t>
+          <t>5060-451-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13111,17 +13111,17 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>72.201.100-7</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE LA ARAUCANIA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K199" t="inlineStr"/>
@@ -13146,7 +13146,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1472.03</v>
+        <v>3810.86</v>
       </c>
     </row>
     <row r="200">
@@ -13282,7 +13282,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>4114-199-CM26</t>
+          <t>4114-201-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13322,32 +13322,28 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>32238.71</v>
+        <v>737.8</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>4114-201-CM26</t>
+          <t>4114-199-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13387,22 +13383,26 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>737.8</v>
+        <v>32238.71</v>
       </c>
     </row>
     <row r="204">
@@ -13473,7 +13473,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>4179-889-CM26</t>
+          <t>3494-235-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13498,12 +13498,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>69.190.800-3</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>I MUNICIPALIDAD DE VILCUN</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13513,17 +13513,17 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -13532,13 +13532,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>736.37</v>
+        <v>6538.24</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>3494-235-CM26</t>
+          <t>4179-889-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>69.190.800-3</t>
+          <t>69.190.100-9</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILCUN</t>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13578,17 +13578,17 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -13597,7 +13597,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>6538.24</v>
+        <v>736.37</v>
       </c>
     </row>
     <row r="207">
@@ -13733,7 +13733,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>4406-665-CM26</t>
+          <t>3887-274-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13758,12 +13758,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.180.800-9</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Lumaco</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13773,32 +13773,28 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>comercializadora TecnoImport SpA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3262.36</v>
+        <v>102.33</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3887-274-CM26</t>
+          <t>4406-665-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13823,12 +13819,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.180.800-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13838,22 +13834,26 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr"/>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>102.33</v>
+        <v>3262.36</v>
       </c>
     </row>
     <row r="211">
@@ -13924,7 +13924,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>960855-21-CM26</t>
+          <t>3922-719-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13944,17 +13944,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.180.500-K</t>
+          <t>69.191.500-K</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -13964,12 +13964,12 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>RyC Servicios Computacionales Ltda</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>79.968.900-6</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -13979,13 +13979,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>2776.15</v>
+        <v>2475.2</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>3922-718-CM26</t>
+          <t>960855-21-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14005,17 +14005,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>69.191.500-K</t>
+          <t>69.180.500-K</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14025,32 +14025,28 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>816.71</v>
+        <v>2776.15</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3922-719-CM26</t>
+          <t>3922-718-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14090,22 +14086,26 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>RyC Servicios Computacionales Ltda</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>79.968.900-6</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr"/>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2475.2</v>
+        <v>816.71</v>
       </c>
     </row>
     <row r="215">
@@ -14932,7 +14932,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3518-373-CM26</t>
+          <t>765-189-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -14952,17 +14952,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.180.700-2</t>
+          <t>72.396.000-2</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14972,28 +14972,32 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr"/>
+          <t>76.128.275-1</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1868.18</v>
+        <v>6717.5</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>765-189-CM26</t>
+          <t>3518-373-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15013,17 +15017,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>72.396.000-2</t>
+          <t>69.180.700-2</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>CORP NACIONAL DE DESARROLLO INDIGENA</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15033,26 +15037,22 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>6717.5</v>
+        <v>1868.18</v>
       </c>
     </row>
     <row r="230">
@@ -15687,6 +15687,67 @@
       </c>
       <c r="M239" s="2" t="n">
         <v>7034.93</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>5060-887-CM26</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Sociedad Comercial Infostore Ltda</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="n">
+        <v>892.49</v>
       </c>
     </row>
   </sheetData>
